--- a/data/trans_bre/P26-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P26-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 4,36</t>
+          <t>-8,23; 4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 6,03</t>
+          <t>-8,51; 5,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 3,78</t>
+          <t>-10,04; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 11,39</t>
+          <t>-8,29; 12,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 9,62</t>
+          <t>-15,85; 10,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 12,07</t>
+          <t>-15,0; 11,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 11,3</t>
+          <t>-23,09; 8,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 76,65</t>
+          <t>-33,11; 88,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,81</t>
+          <t>1,79; 13,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 7,05</t>
+          <t>-3,79; 7,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 10,57</t>
+          <t>-1,36; 10,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 7,08</t>
+          <t>-8,64; 6,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 41,14</t>
+          <t>4,79; 41,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 19,76</t>
+          <t>-9,12; 21,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 37,37</t>
+          <t>-4,06; 35,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 51,68</t>
+          <t>-41,45; 47,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 22,07</t>
+          <t>11,42; 21,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 14,15</t>
+          <t>3,35; 13,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,16</t>
+          <t>-2,34; 7,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,27</t>
+          <t>1,34; 8,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,42; 108,91</t>
+          <t>43,32; 104,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 49,43</t>
+          <t>9,54; 47,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 33,11</t>
+          <t>-9,3; 31,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,32; 117,46</t>
+          <t>11,39; 116,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 18,49</t>
+          <t>6,18; 18,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 19,37</t>
+          <t>7,34; 19,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 9,03</t>
+          <t>-1,03; 9,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,28; 3,73</t>
+          <t>-60,33; 3,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,69; 67,04</t>
+          <t>18,02; 71,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 63,31</t>
+          <t>18,83; 65,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 39,83</t>
+          <t>-3,73; 45,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 35,42</t>
+          <t>-81,9; 32,85</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 17,08</t>
+          <t>3,67; 17,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 16,79</t>
+          <t>2,51; 16,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,21</t>
+          <t>-3,96; 7,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,98</t>
+          <t>-3,24; 4,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,96; 92,96</t>
+          <t>14,09; 89,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 71,92</t>
+          <t>7,91; 71,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 36,05</t>
+          <t>-15,43; 37,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 38,62</t>
+          <t>-22,23; 40,69</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,87</t>
+          <t>4,39; 15,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 11,79</t>
+          <t>-1,47; 12,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 6,66</t>
+          <t>-4,45; 6,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 4,09</t>
+          <t>-6,08; 4,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,94; 202,45</t>
+          <t>33,37; 232,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 79,43</t>
+          <t>-7,35; 85,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 65,91</t>
+          <t>-29,22; 66,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 64,91</t>
+          <t>-71,38; 70,41</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 13,49</t>
+          <t>-1,2; 13,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 12,85</t>
+          <t>0,56; 12,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,15</t>
+          <t>-1,06; 8,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,01</t>
+          <t>2,41; 7,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 175,19</t>
+          <t>-10,77; 181,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 170,45</t>
+          <t>2,95; 171,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 209,4</t>
+          <t>-16,76; 186,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69,62; 1226,0</t>
+          <t>49,61; 1155,52</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,12</t>
+          <t>6,25; 10,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,21</t>
+          <t>3,48; 8,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,66</t>
+          <t>-0,67; 3,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 1,91</t>
+          <t>-28,66; 1,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,02; 40,75</t>
+          <t>20,94; 39,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,83; 25,92</t>
+          <t>10,03; 26,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 15,11</t>
+          <t>-2,56; 15,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 16,58</t>
+          <t>-72,31; 16,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P26-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P26-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 4,85</t>
+          <t>-7,76; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 5,52</t>
+          <t>-7,91; 6,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 3,26</t>
+          <t>-10,33; 3,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 12,41</t>
+          <t>-8,48; 9,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 10,37</t>
+          <t>-14,99; 10,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 11,15</t>
+          <t>-14,01; 12,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 8,89</t>
+          <t>-24,21; 9,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 88,79</t>
+          <t>-35,04; 62,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>-0,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 13,16</t>
+          <t>1,9; 13,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,5</t>
+          <t>-4,12; 7,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 10,17</t>
+          <t>-0,92; 10,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 6,39</t>
+          <t>-6,64; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 41,82</t>
+          <t>5,54; 42,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 21,35</t>
+          <t>-9,88; 19,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 35,88</t>
+          <t>-3,27; 36,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 47,92</t>
+          <t>-30,95; 44,54</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 21,82</t>
+          <t>11,28; 21,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,56</t>
+          <t>3,5; 13,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,28</t>
+          <t>-2,72; 7,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,47</t>
+          <t>1,74; 8,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,32; 104,84</t>
+          <t>43,19; 106,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 47,14</t>
+          <t>10,11; 47,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 31,75</t>
+          <t>-9,93; 33,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 116,59</t>
+          <t>18,14; 134,84</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-24,12</t>
+          <t>3,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-63,71%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 18,95</t>
+          <t>6,19; 19,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 19,97</t>
+          <t>7,23; 19,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 9,63</t>
+          <t>-0,69; 9,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,33; 3,44</t>
+          <t>-1,04; 6,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 71,09</t>
+          <t>19,46; 73,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 65,09</t>
+          <t>19,58; 63,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 45,83</t>
+          <t>-2,73; 42,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,9; 32,85</t>
+          <t>-7,77; 68,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 17,23</t>
+          <t>4,49; 17,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 16,54</t>
+          <t>2,97; 16,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 7,71</t>
+          <t>-4,62; 7,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,19</t>
+          <t>-2,69; 3,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 89,2</t>
+          <t>17,35; 89,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 71,02</t>
+          <t>10,27; 73,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 37,79</t>
+          <t>-17,32; 37,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 40,69</t>
+          <t>-18,88; 39,15</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,19%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 15,76</t>
+          <t>4,43; 15,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 12,21</t>
+          <t>-1,33; 11,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 6,47</t>
+          <t>-4,57; 6,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 4,28</t>
+          <t>-0,31; 6,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,37; 232,04</t>
+          <t>32,78; 228,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 85,01</t>
+          <t>-6,7; 79,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 66,36</t>
+          <t>-30,86; 69,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 70,41</t>
+          <t>-4,48; 124,78</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>333,15%</t>
+          <t>332,23%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 13,35</t>
+          <t>-0,89; 13,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 12,95</t>
+          <t>0,85; 13,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 8,7</t>
+          <t>-1,1; 8,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,03</t>
+          <t>2,33; 7,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 181,52</t>
+          <t>-7,27; 190,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 171,08</t>
+          <t>3,71; 188,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 186,0</t>
+          <t>-13,57; 180,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49,61; 1155,52</t>
+          <t>62,11; 1172,66</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-30,36%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,93</t>
+          <t>6,1; 11,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,32</t>
+          <t>3,44; 8,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,75</t>
+          <t>-0,47; 3,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 1,85</t>
+          <t>0,46; 3,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,94; 39,62</t>
+          <t>20,41; 39,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 26,19</t>
+          <t>10,35; 26,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 15,44</t>
+          <t>-2,04; 15,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 16,22</t>
+          <t>3,67; 36,2</t>
         </is>
       </c>
     </row>
